--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="28800" windowHeight="13720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -870,10 +870,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1542,7 +1545,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
@@ -1559,7 +1562,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -1576,7 +1579,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B21" t="s">
         <v>23</v>
@@ -1593,7 +1596,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="2">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
@@ -1610,7 +1613,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="2">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -1627,7 +1630,7 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="2">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -1644,7 +1647,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="2">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -1661,7 +1664,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="2">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -1678,7 +1681,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="2">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
@@ -1694,8 +1697,8 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>46162</v>
+      <c r="A28" s="3">
+        <v>46169</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
   <si>
     <t>date</t>
   </si>
@@ -231,6 +231,12 @@
   </si>
   <si>
     <t>《Make LLM Inference Affordable to Everyone Augmenting GPU Memory with NDP-DIMM》</t>
+  </si>
+  <si>
+    <t>GPU 硬件安全</t>
+  </si>
+  <si>
+    <t>《Spy in the GPU-box: Covert and Side Channel Attacks on Multi-GPU System》</t>
   </si>
   <si>
     <t>待定</t>
@@ -870,13 +876,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1557,7 +1560,7 @@
         <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1571,10 +1574,10 @@
         <v>40</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1588,10 +1591,10 @@
         <v>36</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1605,10 +1608,10 @@
         <v>7</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1622,10 +1625,10 @@
         <v>11</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1639,10 +1642,10 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1656,10 +1659,10 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1673,10 +1676,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1690,14 +1693,14 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3">
+      <c r="A28" s="2">
         <v>46169</v>
       </c>
       <c r="B28" t="s">
@@ -1707,10 +1710,10 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:5">

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13720"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1571,7 +1571,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
         <v>70</v>
@@ -1588,7 +1588,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D21" t="s">
         <v>70</v>
@@ -1605,7 +1605,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
         <v>70</v>
@@ -1622,7 +1622,7 @@
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
         <v>70</v>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="72">
   <si>
     <t>date</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>待定</t>
+  </si>
+  <si>
+    <t>高子璇</t>
   </si>
 </sst>
 </file>
@@ -1717,7 +1720,21 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2"/>
+      <c r="A29" s="2">
+        <v>46176</v>
+      </c>
+      <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" t="s">
+        <v>70</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -1574,7 +1574,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s">
         <v>70</v>
@@ -1591,7 +1591,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D21" t="s">
         <v>70</v>
@@ -1608,7 +1608,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
         <v>70</v>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
   <si>
     <t>date</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t>《Spy in the GPU-box: Covert and Side Channel Attacks on Multi-GPU System》</t>
+  </si>
+  <si>
+    <t>硬件性能评测</t>
+  </si>
+  <si>
+    <t>《Systematic Evaluation of Randomized Cache Designs against Cache Occupancy》</t>
   </si>
   <si>
     <t>待定</t>
@@ -1580,7 +1586,7 @@
         <v>70</v>
       </c>
       <c r="E20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1594,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E21" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1611,10 +1617,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1628,10 +1634,10 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1645,10 +1651,10 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1662,10 +1668,10 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1679,10 +1685,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1696,10 +1702,10 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1713,10 +1719,10 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1727,13 +1733,13 @@
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="77">
   <si>
     <t>date</t>
   </si>
@@ -243,6 +243,15 @@
   </si>
   <si>
     <t>《Systematic Evaluation of Randomized Cache Designs against Cache Occupancy》</t>
+  </si>
+  <si>
+    <t>《High information capacity  DNA-based data storage with augmented encoding characters  using degenerate bases》</t>
+  </si>
+  <si>
+    <t>文件系统</t>
+  </si>
+  <si>
+    <t>《Sharpen the Spec, Cut the Code: A Case for Generative File System with SYSSPEC》</t>
   </si>
   <si>
     <t>待定</t>
@@ -1600,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="D21" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
         <v>72</v>
@@ -1617,10 +1626,10 @@
         <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1634,10 +1643,10 @@
         <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1651,10 +1660,10 @@
         <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1668,10 +1677,10 @@
         <v>24</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1685,10 +1694,10 @@
         <v>28</v>
       </c>
       <c r="D26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E26" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1702,10 +1711,10 @@
         <v>32</v>
       </c>
       <c r="D27" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1719,10 +1728,10 @@
         <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -1733,13 +1742,13 @@
         <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/seminar_schedule.xlsx
+++ b/seminar_schedule.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="28800" windowHeight="12140"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -269,7 +269,7 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="[$-409]yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -894,10 +894,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1276,7 +1280,7 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
@@ -1293,7 +1297,7 @@
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
@@ -1310,7 +1314,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
@@ -1327,7 +1331,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B5" t="s">
@@ -1344,7 +1348,7 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
@@ -1361,7 +1365,7 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
@@ -1378,7 +1382,7 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -1395,7 +1399,7 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
@@ -1412,7 +1416,7 @@
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
@@ -1429,7 +1433,7 @@
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B11" t="s">
@@ -1446,7 +1450,7 @@
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -1463,7 +1467,7 @@
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B13" t="s">
@@ -1480,7 +1484,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B14" t="s">
@@ -1497,7 +1501,7 @@
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B15" t="s">
@@ -1514,7 +1518,7 @@
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B16" t="s">
@@ -1531,7 +1535,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B17" t="s">
@@ -1548,7 +1552,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B18" t="s">
@@ -1565,7 +1569,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2">
+      <c r="A19" s="3">
         <v>46106</v>
       </c>
       <c r="B19" t="s">
@@ -1582,7 +1586,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2">
+      <c r="A20" s="3">
         <v>46113</v>
       </c>
       <c r="B20" t="s">
@@ -1599,7 +1603,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2">
+      <c r="A21" s="3">
         <v>46120</v>
       </c>
       <c r="B21" t="s">
@@ -1616,7 +1620,7 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2">
+      <c r="A22" s="3">
         <v>46127</v>
       </c>
       <c r="B22" t="s">
@@ -1633,8 +1637,8 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="2">
-        <v>46134</v>
+      <c r="A23" s="4">
+        <v>46141</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
@@ -1650,8 +1654,8 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="2">
-        <v>46141</v>
+      <c r="A24" s="4">
+        <v>46148</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
@@ -1667,8 +1671,8 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="2">
-        <v>46148</v>
+      <c r="A25" s="4">
+        <v>46155</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -1684,8 +1688,8 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="2">
-        <v>46155</v>
+      <c r="A26" s="4">
+        <v>46162</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
@@ -1701,8 +1705,8 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="2">
-        <v>46162</v>
+      <c r="A27" s="4">
+        <v>46169</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
@@ -1718,8 +1722,8 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="2">
-        <v>46169</v>
+      <c r="A28" s="4">
+        <v>46176</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
@@ -1735,8 +1739,8 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="2">
-        <v>46176</v>
+      <c r="A29" s="4">
+        <v>46183</v>
       </c>
       <c r="B29" t="s">
         <v>23</v>
